--- a/research/traditional_assets/database/data/iceland/iceland_entertainment.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_entertainment.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>4.405405405405405</v>
+        <v>12.23188405797101</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-4.891891891891892</v>
+        <v>-14.30434782608696</v>
       </c>
       <c r="J2">
-        <v>-4.891891891891892</v>
+        <v>-14.30434782608696</v>
       </c>
       <c r="K2">
-        <v>-0.358</v>
+        <v>-0.543</v>
       </c>
       <c r="L2">
-        <v>-3.225225225225225</v>
+        <v>-7.869565217391305</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,67 +627,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2.89</v>
+        <v>0.868</v>
       </c>
       <c r="V2">
-        <v>0.2778846153846154</v>
+        <v>0.2391184573002755</v>
       </c>
       <c r="W2">
-        <v>-0.03345794392523364</v>
+        <v>-0.05673981191222571</v>
       </c>
       <c r="X2">
-        <v>0.1207443530461866</v>
+        <v>0.09891852205158792</v>
       </c>
       <c r="Y2">
-        <v>-0.1542022969714202</v>
+        <v>-0.1556583339638136</v>
       </c>
       <c r="Z2">
-        <v>0.01031502648452746</v>
+        <v>0.01021919431279621</v>
       </c>
       <c r="AA2">
-        <v>-0.05045999442431002</v>
+        <v>-0.1461789099526067</v>
       </c>
       <c r="AB2">
-        <v>0.1202945520892385</v>
+        <v>0.09819129893397223</v>
       </c>
       <c r="AC2">
-        <v>-0.1707545465135485</v>
+        <v>-0.2443702088865789</v>
       </c>
       <c r="AD2">
-        <v>0.07199999999999999</v>
+        <v>0.055</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.07199999999999999</v>
+        <v>0.055</v>
       </c>
       <c r="AG2">
-        <v>-2.818</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.006875477463712758</v>
+        <v>0.01492537313432836</v>
       </c>
       <c r="AI2">
-        <v>0.0074673304293715</v>
+        <v>0.006183249016301293</v>
       </c>
       <c r="AJ2">
-        <v>-0.3716697441308361</v>
+        <v>-0.288604898828541</v>
       </c>
       <c r="AK2">
-        <v>-0.4173578199052133</v>
+        <v>-0.1012831693036003</v>
       </c>
       <c r="AL2">
-        <v>0.017</v>
+        <v>0.007</v>
       </c>
       <c r="AM2">
-        <v>-0.051</v>
+        <v>-0.09599999999999999</v>
       </c>
       <c r="AO2">
-        <v>-31.94117647058824</v>
+        <v>-141</v>
       </c>
       <c r="AQ2">
-        <v>10.64705882352941</v>
+        <v>10.28125</v>
       </c>
     </row>
     <row r="3">
@@ -707,22 +707,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>4.405405405405405</v>
+        <v>12.23188405797101</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-4.891891891891892</v>
+        <v>-14.30434782608696</v>
       </c>
       <c r="J3">
-        <v>-4.891891891891892</v>
+        <v>-14.30434782608696</v>
       </c>
       <c r="K3">
-        <v>-0.358</v>
+        <v>-0.543</v>
       </c>
       <c r="L3">
-        <v>-3.225225225225225</v>
+        <v>-7.869565217391305</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,67 +746,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.89</v>
+        <v>0.868</v>
       </c>
       <c r="V3">
-        <v>0.2778846153846154</v>
+        <v>0.2391184573002755</v>
       </c>
       <c r="W3">
-        <v>-0.03345794392523364</v>
+        <v>-0.05673981191222571</v>
       </c>
       <c r="X3">
-        <v>0.1207443530461866</v>
+        <v>0.09891852205158792</v>
       </c>
       <c r="Y3">
-        <v>-0.1542022969714202</v>
+        <v>-0.1556583339638136</v>
       </c>
       <c r="Z3">
-        <v>0.01031502648452746</v>
+        <v>0.01021919431279621</v>
       </c>
       <c r="AA3">
-        <v>-0.05045999442431002</v>
+        <v>-0.1461789099526067</v>
       </c>
       <c r="AB3">
-        <v>0.1202945520892385</v>
+        <v>0.09819129893397223</v>
       </c>
       <c r="AC3">
-        <v>-0.1707545465135485</v>
+        <v>-0.2443702088865789</v>
       </c>
       <c r="AD3">
-        <v>0.07199999999999999</v>
+        <v>0.055</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.07199999999999999</v>
+        <v>0.055</v>
       </c>
       <c r="AG3">
-        <v>-2.818</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.006875477463712758</v>
+        <v>0.01492537313432836</v>
       </c>
       <c r="AI3">
-        <v>0.0074673304293715</v>
+        <v>0.006183249016301293</v>
       </c>
       <c r="AJ3">
-        <v>-0.3716697441308361</v>
+        <v>-0.288604898828541</v>
       </c>
       <c r="AK3">
-        <v>-0.4173578199052133</v>
+        <v>-0.1012831693036003</v>
       </c>
       <c r="AL3">
-        <v>0.017</v>
+        <v>0.007</v>
       </c>
       <c r="AM3">
-        <v>-0.051</v>
+        <v>-0.09599999999999999</v>
       </c>
       <c r="AO3">
-        <v>-31.94117647058824</v>
+        <v>-141</v>
       </c>
       <c r="AQ3">
-        <v>10.64705882352941</v>
+        <v>10.28125</v>
       </c>
     </row>
   </sheetData>
